--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10119"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24geschichte/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFAF230-53BE-AF49-80FE-C12F1C15AFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B574440E-3286-9443-B93A-0438DE9B978D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="87">
   <si>
     <t>blank</t>
   </si>
@@ -285,6 +285,15 @@
   </si>
   <si>
     <t>"Thick Description" als ein ethnographischer Ansatz erfassen.</t>
+  </si>
+  <si>
+    <t>Religionssoziologische Fragestellungen an Beispielen aus dem Werk Max Webers erläutern.</t>
+  </si>
+  <si>
+    <t>Ein funktionsorientiertes Modell der Religion nach Bourdieu's Begriffen "Feld", "Kapital" und "Habitus" beschreiben.</t>
+  </si>
+  <si>
+    <t>hainzInterventionInterpretationJacques2008</t>
   </si>
 </sst>
 </file>
@@ -295,9 +304,16 @@
     <numFmt numFmtId="164" formatCode="dd\.mm"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -392,21 +408,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -415,13 +431,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1401,6 +1418,9 @@
       <c r="L12" s="14" t="s">
         <v>49</v>
       </c>
+      <c r="M12" t="s">
+        <v>84</v>
+      </c>
       <c r="N12" t="str">
         <f t="shared" si="4"/>
         <v>[11]</v>
@@ -1453,6 +1473,9 @@
       <c r="L13" s="13" t="s">
         <v>45</v>
       </c>
+      <c r="M13" t="s">
+        <v>85</v>
+      </c>
       <c r="N13" t="str">
         <f t="shared" si="4"/>
         <v>[12]</v>
@@ -1467,7 +1490,7 @@
 ---</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="B14" s="3">
         <v>13</v>
       </c>
@@ -1501,6 +1524,9 @@
       <c r="K14" t="str">
         <f t="shared" si="3"/>
         <v>13-Jacques-Derrida</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>86</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="4"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/24geschichte/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B574440E-3286-9443-B93A-0438DE9B978D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882715DC-EE46-1745-B798-90AF2B5258E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30240" yWindow="2720" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="88">
   <si>
     <t>blank</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>hainzInterventionInterpretationJacques2008</t>
+  </si>
+  <si>
+    <t>Die Relevanz der "Dekonstruktion", des Diskursbegriffs und der "Hermeneutik des Verdachts" für religionskritische Ansätze erläutern.</t>
   </si>
 </sst>
 </file>
@@ -1528,6 +1531,9 @@
       <c r="L14" s="16" t="s">
         <v>86</v>
       </c>
+      <c r="M14" t="s">
+        <v>87</v>
+      </c>
       <c r="N14" t="str">
         <f t="shared" si="4"/>
         <v>[13]</v>
